--- a/data/ready_stocks/galtex-wb-stocks-updated.xlsx
+++ b/data/ready_stocks/galtex-wb-stocks-updated.xlsx
@@ -397,10 +397,1491 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:B185"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Баркод</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Количество</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2041603105073</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2041603105110</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2041603105134</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2041603105158</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2041603105387</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2041603105394</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2041603105400</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2041603105417</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2041603105424</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2041603105431</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>2044186087804</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2041603105455</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2041603105462</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2041603105479</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2041603105486</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2041603105493</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2041603105509</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2041602656262</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2042234857515</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2042234857522</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2042675781165</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2042234857416</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2042234857423</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2042234857492</v>
+      </c>
+      <c r="B25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>2044186087811</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>2044186087828</v>
+      </c>
+      <c r="B27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2043366775043</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2043792548891</v>
+      </c>
+      <c r="B29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2043792548907</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2043792548860</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2043792548938</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2043792548877</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2043792548921</v>
+      </c>
+      <c r="B34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2041603105080</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2041603105127</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2041603105516</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>2041603105523</v>
+      </c>
+      <c r="B38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>2041603105530</v>
+      </c>
+      <c r="B39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>2041603105547</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2041603105554</v>
+      </c>
+      <c r="B41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>2041603105561</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>2041603105578</v>
+      </c>
+      <c r="B43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2042234857485</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>2042234857430</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>2042675781066</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>2042675781073</v>
+      </c>
+      <c r="B47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>2042675781080</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>2042675781097</v>
+      </c>
+      <c r="B49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>2042675781103</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2042675781110</v>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>2042675781127</v>
+      </c>
+      <c r="B52">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>2042234857546</v>
+      </c>
+      <c r="B53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>2042234857454</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>2042675781141</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2042280034557</v>
+      </c>
+      <c r="B56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>2044186087835</v>
+      </c>
+      <c r="B57">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>2044186087842</v>
+      </c>
+      <c r="B58">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>2043366775104</v>
+      </c>
+      <c r="B59">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>2043366775050</v>
+      </c>
+      <c r="B60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>2043366775067</v>
+      </c>
+      <c r="B61">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>2043366775074</v>
+      </c>
+      <c r="B62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>2043366775081</v>
+      </c>
+      <c r="B63">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>2043366775098</v>
+      </c>
+      <c r="B64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>2041603105097</v>
+      </c>
+      <c r="B65">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>2041603105141</v>
+      </c>
+      <c r="B66">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>2041603105165</v>
+      </c>
+      <c r="B67">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>2041603105189</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>2041603105202</v>
+      </c>
+      <c r="B69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>2041603105226</v>
+      </c>
+      <c r="B70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>2041603105233</v>
+      </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>2041603105240</v>
+      </c>
+      <c r="B72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>2041603105257</v>
+      </c>
+      <c r="B73">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>2041603105264</v>
+      </c>
+      <c r="B74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>2041603105288</v>
+      </c>
+      <c r="B75">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>2041603105295</v>
+      </c>
+      <c r="B76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>2041603105318</v>
+      </c>
+      <c r="B77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>2041603105325</v>
+      </c>
+      <c r="B78">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>2041603105332</v>
+      </c>
+      <c r="B79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>2041603105349</v>
+      </c>
+      <c r="B80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>2041603105363</v>
+      </c>
+      <c r="B81">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>2041603105585</v>
+      </c>
+      <c r="B82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>2042675781172</v>
+      </c>
+      <c r="B83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>2042675781189</v>
+      </c>
+      <c r="B84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>2042675781196</v>
+      </c>
+      <c r="B85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>2042675781202</v>
+      </c>
+      <c r="B86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>2042675781219</v>
+      </c>
+      <c r="B87">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>2042675781226</v>
+      </c>
+      <c r="B88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>2042675781233</v>
+      </c>
+      <c r="B89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>2042675781240</v>
+      </c>
+      <c r="B90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>2042675781257</v>
+      </c>
+      <c r="B91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>2042675781264</v>
+      </c>
+      <c r="B92">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>2041603105301</v>
+      </c>
+      <c r="B93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>2041603105271</v>
+      </c>
+      <c r="B94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>2041603105066</v>
+      </c>
+      <c r="B95">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>2043401357265</v>
+      </c>
+      <c r="B96">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>2042793570610</v>
+      </c>
+      <c r="B97">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>2043401357197</v>
+      </c>
+      <c r="B98">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>2043401281201</v>
+      </c>
+      <c r="B99">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>2043401281096</v>
+      </c>
+      <c r="B100">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>2043401357234</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>2043401357258</v>
+      </c>
+      <c r="B102">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>2043401281324</v>
+      </c>
+      <c r="B103">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>2043401281218</v>
+      </c>
+      <c r="B104">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>2043401357296</v>
+      </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>2043401281263</v>
+      </c>
+      <c r="B106">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>2043401281140</v>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>2043401357210</v>
+      </c>
+      <c r="B108">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>2043401281157</v>
+      </c>
+      <c r="B109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>2043401281256</v>
+      </c>
+      <c r="B110">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>2043401281188</v>
+      </c>
+      <c r="B111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>2042793570641</v>
+      </c>
+      <c r="B112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>2043401357203</v>
+      </c>
+      <c r="B113">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>2043401281195</v>
+      </c>
+      <c r="B114">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>2043401281171</v>
+      </c>
+      <c r="B115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>2044222856241</v>
+      </c>
+      <c r="B116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>2043401281041</v>
+      </c>
+      <c r="B117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>2042793570597</v>
+      </c>
+      <c r="B118">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>2043401281003</v>
+      </c>
+      <c r="B119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>2043401281072</v>
+      </c>
+      <c r="B120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>2043401281089</v>
+      </c>
+      <c r="B121">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>2043401281102</v>
+      </c>
+      <c r="B122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>2043401281027</v>
+      </c>
+      <c r="B123">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>2043401281058</v>
+      </c>
+      <c r="B124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>2043401281133</v>
+      </c>
+      <c r="B125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>2042793570627</v>
+      </c>
+      <c r="B126">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>2043401357265</v>
+      </c>
+      <c r="B127">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>2043401281232</v>
+      </c>
+      <c r="B128">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>2043401357272</v>
+      </c>
+      <c r="B129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>2043401281225</v>
+      </c>
+      <c r="B130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>2042793570634</v>
+      </c>
+      <c r="B131">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>2042793570603</v>
+      </c>
+      <c r="B132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>2043401281294</v>
+      </c>
+      <c r="B133">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>2043401357227</v>
+      </c>
+      <c r="B134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>2043401281249</v>
+      </c>
+      <c r="B135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>2043401281164</v>
+      </c>
+      <c r="B136">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>2043401357289</v>
+      </c>
+      <c r="B137">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>2043401281119</v>
+      </c>
+      <c r="B138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>2043401281126</v>
+      </c>
+      <c r="B139">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>2043401281065</v>
+      </c>
+      <c r="B140">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>2043401357302</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>2044389037231</v>
+      </c>
+      <c r="B142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>2044389037255</v>
+      </c>
+      <c r="B143">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>2041603105370</v>
+      </c>
+      <c r="B144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>2044389037347</v>
+      </c>
+      <c r="B145">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>2044389037361</v>
+      </c>
+      <c r="B146">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>2044389037385</v>
+      </c>
+      <c r="B147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>2044389037859</v>
+      </c>
+      <c r="B148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>2044389037606</v>
+      </c>
+      <c r="B149">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>2044389037651</v>
+      </c>
+      <c r="B150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>2044389037682</v>
+      </c>
+      <c r="B151">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>2044389037736</v>
+      </c>
+      <c r="B152">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>2044389037811</v>
+      </c>
+      <c r="B153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>2044607193725</v>
+      </c>
+      <c r="B154">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>2044607193688</v>
+      </c>
+      <c r="B155">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>2044607193718</v>
+      </c>
+      <c r="B156">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>2044607193664</v>
+      </c>
+      <c r="B157">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>2044607193695</v>
+      </c>
+      <c r="B158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>2044607193701</v>
+      </c>
+      <c r="B159">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>2045447992721</v>
+      </c>
+      <c r="B160">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>2045447992738</v>
+      </c>
+      <c r="B161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>2045447992745</v>
+      </c>
+      <c r="B162">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>2045447992752</v>
+      </c>
+      <c r="B163">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>2045447992776</v>
+      </c>
+      <c r="B164">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <v>2045447992783</v>
+      </c>
+      <c r="B165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>2045447992790</v>
+      </c>
+      <c r="B166">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>2045447992806</v>
+      </c>
+      <c r="B167">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>2045447863069</v>
+      </c>
+      <c r="B168">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>2045447863076</v>
+      </c>
+      <c r="B169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>2045447863083</v>
+      </c>
+      <c r="B170">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>2045447863090</v>
+      </c>
+      <c r="B171">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>2045447863106</v>
+      </c>
+      <c r="B172">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>2045447863113</v>
+      </c>
+      <c r="B173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>2045447863120</v>
+      </c>
+      <c r="B174">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>2045447863137</v>
+      </c>
+      <c r="B175">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176">
+        <v>2045510978966</v>
+      </c>
+      <c r="B176">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>2045510894709</v>
+      </c>
+      <c r="B177">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <v>2046874095344</v>
+      </c>
+      <c r="B178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <v>2046874095610</v>
+      </c>
+      <c r="B179">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <v>2046874095634</v>
+      </c>
+      <c r="B180">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181">
+        <v>2046874095641</v>
+      </c>
+      <c r="B181">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182">
+        <v>2046874457357</v>
+      </c>
+      <c r="B182">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183">
+        <v>2046874457401</v>
+      </c>
+      <c r="B183">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184">
+        <v>2046874457340</v>
+      </c>
+      <c r="B184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185">
+        <v>2046874457395</v>
+      </c>
+      <c r="B185">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B185"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/ready_stocks/galtex-wb-stocks-updated.xlsx
+++ b/data/ready_stocks/galtex-wb-stocks-updated.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B200"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -408,136 +408,1600 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>2047333260518</v>
+      <c r="A2" t="str">
+        <v>2041603105073</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2047333260525</v>
+      <c r="A3" t="str">
+        <v>2041603105110</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>2047333260532</v>
+      <c r="A4" t="str">
+        <v>2041603105134</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>2047333260549</v>
+      <c r="A5" t="str">
+        <v>2041603105158</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>2047333260556</v>
+      <c r="A6" t="str">
+        <v>2041603105387</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>2047333260563</v>
+      <c r="A7" t="str">
+        <v>2041603105394</v>
       </c>
       <c r="B7">
         <v>5</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>2047333260570</v>
+      <c r="A8" t="str">
+        <v>2041603105400</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>2047333260587</v>
+      <c r="A9" t="str">
+        <v>2041603105417</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>2047333260594</v>
+      <c r="A10" t="str">
+        <v>2041603105424</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>2047333260600</v>
+      <c r="A11" t="str">
+        <v>2041603105431</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>2047333260617</v>
+        <v>2044186087804</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>2047333260624</v>
+      <c r="A13" t="str">
+        <v>2041603105455</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>2047333260631</v>
+      <c r="A14" t="str">
+        <v>2041603105462</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>2047333260648</v>
+      <c r="A15" t="str">
+        <v>2041603105479</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>2047333260655</v>
+      <c r="A16" t="str">
+        <v>2041603105486</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>2047333260662</v>
+      <c r="A17" t="str">
+        <v>2041603105493</v>
       </c>
       <c r="B17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2041603105509</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2041602656262</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2042234857515</v>
+      </c>
+      <c r="B20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2042234857522</v>
+      </c>
+      <c r="B21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2042675781165</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2042234857416</v>
+      </c>
+      <c r="B23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2042234857423</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2042234857492</v>
+      </c>
+      <c r="B25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>2044186087811</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>2044186087828</v>
+      </c>
+      <c r="B27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2043366775043</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2043792548891</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2043792548907</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2043792548860</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2043792548938</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2043792548877</v>
+      </c>
+      <c r="B33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2043792548921</v>
+      </c>
+      <c r="B34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2041603105080</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2041603105127</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2041603105516</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>2041603105523</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>2041603105530</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>2041603105547</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2041603105554</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>2041603105561</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>2041603105578</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2042234857485</v>
+      </c>
+      <c r="B44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>2042234857430</v>
+      </c>
+      <c r="B45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>2042675781066</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>2042675781073</v>
+      </c>
+      <c r="B47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>2042675781080</v>
+      </c>
+      <c r="B48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>2042675781097</v>
+      </c>
+      <c r="B49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>2042675781103</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2042675781110</v>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>2042675781127</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>2042234857546</v>
+      </c>
+      <c r="B53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>2042234857454</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>2042675781141</v>
+      </c>
+      <c r="B55">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2042280034557</v>
+      </c>
+      <c r="B56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>2044186087835</v>
+      </c>
+      <c r="B57">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>2044186087842</v>
+      </c>
+      <c r="B58">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>2043366775104</v>
+      </c>
+      <c r="B59">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>2043366775050</v>
+      </c>
+      <c r="B60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>2043366775067</v>
+      </c>
+      <c r="B61">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>2043366775074</v>
+      </c>
+      <c r="B62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>2043366775081</v>
+      </c>
+      <c r="B63">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>2043366775098</v>
+      </c>
+      <c r="B64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>2041603105097</v>
+      </c>
+      <c r="B65">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>2041603105141</v>
+      </c>
+      <c r="B66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>2041603105165</v>
+      </c>
+      <c r="B67">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>2041603105189</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>2041603105202</v>
+      </c>
+      <c r="B69">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>2041603105226</v>
+      </c>
+      <c r="B70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>2041603105233</v>
+      </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>2041603105240</v>
+      </c>
+      <c r="B72">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>2041603105257</v>
+      </c>
+      <c r="B73">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>2041603105264</v>
+      </c>
+      <c r="B74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>2041603105288</v>
+      </c>
+      <c r="B75">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>2041603105295</v>
+      </c>
+      <c r="B76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>2041603105318</v>
+      </c>
+      <c r="B77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>2041603105325</v>
+      </c>
+      <c r="B78">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>2041603105332</v>
+      </c>
+      <c r="B79">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>2041603105349</v>
+      </c>
+      <c r="B80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>2041603105363</v>
+      </c>
+      <c r="B81">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>2041603105585</v>
+      </c>
+      <c r="B82">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>2042675781172</v>
+      </c>
+      <c r="B83">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>2042675781189</v>
+      </c>
+      <c r="B84">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>2042675781196</v>
+      </c>
+      <c r="B85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>2042675781202</v>
+      </c>
+      <c r="B86">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>2042675781219</v>
+      </c>
+      <c r="B87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>2042675781226</v>
+      </c>
+      <c r="B88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>2042675781233</v>
+      </c>
+      <c r="B89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>2042675781240</v>
+      </c>
+      <c r="B90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>2042675781257</v>
+      </c>
+      <c r="B91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>2042675781264</v>
+      </c>
+      <c r="B92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>2041603105301</v>
+      </c>
+      <c r="B93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>2041603105271</v>
+      </c>
+      <c r="B94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>2041603105066</v>
+      </c>
+      <c r="B95">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>2043401357265</v>
+      </c>
+      <c r="B96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>2042793570610</v>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>2043401357197</v>
+      </c>
+      <c r="B98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>2043401281201</v>
+      </c>
+      <c r="B99">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>2043401281096</v>
+      </c>
+      <c r="B100">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>2043401357234</v>
+      </c>
+      <c r="B101">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>2043401357258</v>
+      </c>
+      <c r="B102">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>2043401281324</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>2043401281218</v>
+      </c>
+      <c r="B104">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>2043401357296</v>
+      </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>2043401281263</v>
+      </c>
+      <c r="B106">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>2043401281140</v>
+      </c>
+      <c r="B107">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>2043401357210</v>
+      </c>
+      <c r="B108">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>2043401281157</v>
+      </c>
+      <c r="B109">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>2043401281256</v>
+      </c>
+      <c r="B110">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>2043401281188</v>
+      </c>
+      <c r="B111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>2047418390512</v>
+      </c>
+      <c r="B112">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>2042793570641</v>
+      </c>
+      <c r="B113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>2043401357203</v>
+      </c>
+      <c r="B114">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>2043401281195</v>
+      </c>
+      <c r="B115">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>2043401281171</v>
+      </c>
+      <c r="B116">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>2044222856241</v>
+      </c>
+      <c r="B117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>2043401281041</v>
+      </c>
+      <c r="B118">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>2042793570597</v>
+      </c>
+      <c r="B119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>2043401281003</v>
+      </c>
+      <c r="B120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>2043401281072</v>
+      </c>
+      <c r="B121">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>2043401281089</v>
+      </c>
+      <c r="B122">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>2043401281102</v>
+      </c>
+      <c r="B123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>2043401281027</v>
+      </c>
+      <c r="B124">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>2043401281058</v>
+      </c>
+      <c r="B125">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>2043401281133</v>
+      </c>
+      <c r="B126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>2042793570627</v>
+      </c>
+      <c r="B127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>2043401357265</v>
+      </c>
+      <c r="B128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>2043401281232</v>
+      </c>
+      <c r="B129">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>2043401357272</v>
+      </c>
+      <c r="B130">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>2043401281225</v>
+      </c>
+      <c r="B131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>2042793570634</v>
+      </c>
+      <c r="B132">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>2042793570603</v>
+      </c>
+      <c r="B133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>2043401281294</v>
+      </c>
+      <c r="B134">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>2043401357227</v>
+      </c>
+      <c r="B135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>2043401281249</v>
+      </c>
+      <c r="B136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>2043401281164</v>
+      </c>
+      <c r="B137">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>2043401357289</v>
+      </c>
+      <c r="B138">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>2043401281119</v>
+      </c>
+      <c r="B139">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>2043401281126</v>
+      </c>
+      <c r="B140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>2043401281065</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>2043401357302</v>
+      </c>
+      <c r="B142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>2044389037231</v>
+      </c>
+      <c r="B143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>2044389037255</v>
+      </c>
+      <c r="B144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>2041603105370</v>
+      </c>
+      <c r="B145">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>2044389037347</v>
+      </c>
+      <c r="B146">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>2044389037361</v>
+      </c>
+      <c r="B147">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>2044389037385</v>
+      </c>
+      <c r="B148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>2044389037859</v>
+      </c>
+      <c r="B149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>2044389037606</v>
+      </c>
+      <c r="B150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>2044389037651</v>
+      </c>
+      <c r="B151">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>2044389037682</v>
+      </c>
+      <c r="B152">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>2044389037736</v>
+      </c>
+      <c r="B153">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>2044389037811</v>
+      </c>
+      <c r="B154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>2044607193725</v>
+      </c>
+      <c r="B155">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>2044607193688</v>
+      </c>
+      <c r="B156">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>2044607193718</v>
+      </c>
+      <c r="B157">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>2044607193664</v>
+      </c>
+      <c r="B158">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>2044607193695</v>
+      </c>
+      <c r="B159">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>2044607193701</v>
+      </c>
+      <c r="B160">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>2045447992721</v>
+      </c>
+      <c r="B161">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>2045447992738</v>
+      </c>
+      <c r="B162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>2045447992745</v>
+      </c>
+      <c r="B163">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>2045447992752</v>
+      </c>
+      <c r="B164">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <v>2045447992776</v>
+      </c>
+      <c r="B165">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>2045447992783</v>
+      </c>
+      <c r="B166">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>2045447992790</v>
+      </c>
+      <c r="B167">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>2045447992806</v>
+      </c>
+      <c r="B168">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>2045447863069</v>
+      </c>
+      <c r="B169">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>2045447863076</v>
+      </c>
+      <c r="B170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>2045447863083</v>
+      </c>
+      <c r="B171">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>2045447863090</v>
+      </c>
+      <c r="B172">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>2045447863106</v>
+      </c>
+      <c r="B173">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>2045447863113</v>
+      </c>
+      <c r="B174">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>2045447863120</v>
+      </c>
+      <c r="B175">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176">
+        <v>2045447863137</v>
+      </c>
+      <c r="B176">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>2045510978966</v>
+      </c>
+      <c r="B177">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <v>2045510894709</v>
+      </c>
+      <c r="B178">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <v>2046874095344</v>
+      </c>
+      <c r="B179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <v>2046874095610</v>
+      </c>
+      <c r="B180">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181">
+        <v>2046874095634</v>
+      </c>
+      <c r="B181">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182">
+        <v>2046874095641</v>
+      </c>
+      <c r="B182">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183">
+        <v>2046874457357</v>
+      </c>
+      <c r="B183">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184">
+        <v>2046874457401</v>
+      </c>
+      <c r="B184">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185">
+        <v>2046874457340</v>
+      </c>
+      <c r="B185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186">
+        <v>2046874457395</v>
+      </c>
+      <c r="B186">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187">
+        <v>2047404870929</v>
+      </c>
+      <c r="B187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188">
+        <v>2047404870936</v>
+      </c>
+      <c r="B188">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <v>2047404870974</v>
+      </c>
+      <c r="B189">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <v>2047396898048</v>
+      </c>
+      <c r="B190">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <v>2047396898017</v>
+      </c>
+      <c r="B191">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <v>2047396898079</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>2048856638334</v>
+      </c>
+      <c r="B193">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <v>2048856638303</v>
+      </c>
+      <c r="B194">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195">
+        <v>2048856638310</v>
+      </c>
+      <c r="B195">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196">
+        <v>2048856638389</v>
+      </c>
+      <c r="B196">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197">
+        <v>2048856638365</v>
+      </c>
+      <c r="B197">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198">
+        <v>2048856638358</v>
+      </c>
+      <c r="B198">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199">
+        <v>2048856638372</v>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200">
+        <v>2048856638341</v>
+      </c>
+      <c r="B200">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/ready_stocks/galtex-wb-stocks-updated.xlsx
+++ b/data/ready_stocks/galtex-wb-stocks-updated.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B200"/>
+  <dimension ref="A1:B198"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -409,15 +409,15 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2041603105073</v>
+        <v>2041603105134</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2041603105110</v>
+        <v>2041603105158</v>
       </c>
       <c r="B3">
         <v>5</v>
@@ -425,15 +425,15 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2041603105134</v>
+        <v>2041603105387</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2041603105158</v>
+        <v>2041603105394</v>
       </c>
       <c r="B5">
         <v>5</v>
@@ -441,7 +441,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2041603105387</v>
+        <v>2041603105400</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -449,63 +449,63 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2041603105394</v>
+        <v>2041603105417</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2041603105400</v>
+        <v>2041603105424</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2041603105417</v>
+        <v>2041603105431</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>2041603105424</v>
+      <c r="A10">
+        <v>2044186087804</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2041603105431</v>
+        <v>2041603105455</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>2044186087804</v>
+      <c r="A12" t="str">
+        <v>2041603105462</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2041603105455</v>
+        <v>2041603105479</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2041603105462</v>
+        <v>2041603105486</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -513,7 +513,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2041603105479</v>
+        <v>2041603105493</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -521,23 +521,23 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2041603105486</v>
+        <v>2041603105509</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2041603105493</v>
+        <v>2041602656262</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2041603105509</v>
+        <v>2042234857515</v>
       </c>
       <c r="B18">
         <v>5</v>
@@ -545,7 +545,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2041602656262</v>
+        <v>2042234857522</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -553,15 +553,15 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2042234857515</v>
+        <v>2042675781165</v>
       </c>
       <c r="B20">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2042234857522</v>
+        <v>2042234857416</v>
       </c>
       <c r="B21">
         <v>5</v>
@@ -569,55 +569,55 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2042675781165</v>
+        <v>2042234857423</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2042234857416</v>
+        <v>2042234857492</v>
       </c>
       <c r="B23">
         <v>5</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str">
-        <v>2042234857423</v>
+      <c r="A24">
+        <v>2044186087811</v>
       </c>
       <c r="B24">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
-        <v>2042234857492</v>
+      <c r="A25">
+        <v>2044186087828</v>
       </c>
       <c r="B25">
         <v>5</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>2044186087811</v>
+      <c r="A26" t="str">
+        <v>2043366775043</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>2044186087828</v>
+      <c r="A27" t="str">
+        <v>2043792548891</v>
       </c>
       <c r="B27">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2043366775043</v>
+        <v>2043792548907</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -625,7 +625,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2043792548891</v>
+        <v>2043792548860</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -633,7 +633,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2043792548907</v>
+        <v>2043792548938</v>
       </c>
       <c r="B30">
         <v>5</v>
@@ -641,23 +641,23 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2043792548860</v>
+        <v>2043792548877</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2043792548938</v>
+        <v>2043792548921</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2043792548877</v>
+        <v>2041603105080</v>
       </c>
       <c r="B33">
         <v>5</v>
@@ -665,15 +665,15 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2043792548921</v>
+        <v>2041603105127</v>
       </c>
       <c r="B34">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2041603105080</v>
+        <v>2041603105516</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -681,7 +681,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2041603105127</v>
+        <v>2041603105523</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -689,7 +689,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2041603105516</v>
+        <v>2041603105530</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -697,7 +697,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2041603105523</v>
+        <v>2041603105547</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -705,7 +705,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2041603105530</v>
+        <v>2041603105554</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -713,7 +713,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2041603105547</v>
+        <v>2041603105561</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -721,79 +721,79 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2041603105554</v>
+        <v>2041603105578</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2041603105561</v>
+        <v>2042234857485</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2041603105578</v>
+        <v>2042234857430</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2042234857485</v>
+        <v>2042675781066</v>
       </c>
       <c r="B44">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2042234857430</v>
+        <v>2042675781073</v>
       </c>
       <c r="B45">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2042675781066</v>
+        <v>2042675781080</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2042675781073</v>
+        <v>2042675781097</v>
       </c>
       <c r="B47">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2042675781080</v>
+        <v>2042675781103</v>
       </c>
       <c r="B48">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2042675781097</v>
+        <v>2042675781110</v>
       </c>
       <c r="B49">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2042675781103</v>
+        <v>2042675781127</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -801,15 +801,15 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2042675781110</v>
+        <v>2042234857546</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2042675781127</v>
+        <v>2042234857454</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -817,7 +817,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2042234857546</v>
+        <v>2042675781141</v>
       </c>
       <c r="B53">
         <v>5</v>
@@ -825,39 +825,39 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2042234857454</v>
+        <v>2042280034557</v>
       </c>
       <c r="B54">
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="str">
-        <v>2042675781141</v>
+      <c r="A55">
+        <v>2044186087835</v>
       </c>
       <c r="B55">
         <v>5</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="str">
-        <v>2042280034557</v>
+      <c r="A56">
+        <v>2044186087842</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57">
-        <v>2044186087835</v>
+      <c r="A57" t="str">
+        <v>2043366775104</v>
       </c>
       <c r="B57">
         <v>5</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58">
-        <v>2044186087842</v>
+      <c r="A58" t="str">
+        <v>2043366775050</v>
       </c>
       <c r="B58">
         <v>5</v>
@@ -865,7 +865,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2043366775104</v>
+        <v>2043366775067</v>
       </c>
       <c r="B59">
         <v>5</v>
@@ -873,15 +873,15 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2043366775050</v>
+        <v>2043366775074</v>
       </c>
       <c r="B60">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2043366775067</v>
+        <v>2043366775081</v>
       </c>
       <c r="B61">
         <v>5</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2043366775074</v>
+        <v>2043366775098</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2043366775081</v>
+        <v>2041603105097</v>
       </c>
       <c r="B63">
         <v>5</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2043366775098</v>
+        <v>2041603105141</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -913,7 +913,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2041603105097</v>
+        <v>2041603105165</v>
       </c>
       <c r="B65">
         <v>5</v>
@@ -921,15 +921,15 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2041603105141</v>
+        <v>2041603105189</v>
       </c>
       <c r="B66">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2041603105165</v>
+        <v>2041603105202</v>
       </c>
       <c r="B67">
         <v>5</v>
@@ -937,7 +937,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2041603105189</v>
+        <v>2041603105226</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -945,23 +945,23 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2041603105202</v>
+        <v>2041603105233</v>
       </c>
       <c r="B69">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2041603105226</v>
+        <v>2041603105240</v>
       </c>
       <c r="B70">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2041603105233</v>
+        <v>2041603105257</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -969,15 +969,15 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2041603105240</v>
+        <v>2041603105264</v>
       </c>
       <c r="B72">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2041603105257</v>
+        <v>2041603105288</v>
       </c>
       <c r="B73">
         <v>5</v>
@@ -985,7 +985,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2041603105264</v>
+        <v>2041603105295</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -993,23 +993,23 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2041603105288</v>
+        <v>2041603105318</v>
       </c>
       <c r="B75">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2041603105295</v>
+        <v>2041603105325</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2041603105318</v>
+        <v>2041603105332</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1017,15 +1017,15 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2041603105325</v>
+        <v>2041603105349</v>
       </c>
       <c r="B78">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2041603105332</v>
+        <v>2041603105363</v>
       </c>
       <c r="B79">
         <v>5</v>
@@ -1033,15 +1033,15 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2041603105349</v>
+        <v>2041603105585</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2041603105363</v>
+        <v>2042675781172</v>
       </c>
       <c r="B81">
         <v>5</v>
@@ -1049,7 +1049,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2041603105585</v>
+        <v>2042675781189</v>
       </c>
       <c r="B82">
         <v>5</v>
@@ -1057,15 +1057,15 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2042675781172</v>
+        <v>2042675781196</v>
       </c>
       <c r="B83">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2042675781189</v>
+        <v>2042675781202</v>
       </c>
       <c r="B84">
         <v>5</v>
@@ -1073,23 +1073,23 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>2042675781196</v>
+        <v>2042675781219</v>
       </c>
       <c r="B85">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>2042675781202</v>
+        <v>2042675781226</v>
       </c>
       <c r="B86">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>2042675781219</v>
+        <v>2042675781233</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1097,7 +1097,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>2042675781226</v>
+        <v>2042675781240</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>2042675781233</v>
+        <v>2042675781257</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1113,23 +1113,23 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>2042675781240</v>
+        <v>2042675781264</v>
       </c>
       <c r="B90">
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="str">
-        <v>2042675781257</v>
+      <c r="A91">
+        <v>2041603105301</v>
       </c>
       <c r="B91">
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="str">
-        <v>2042675781264</v>
+      <c r="A92">
+        <v>2041603105271</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1137,15 +1137,15 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>2041603105301</v>
+        <v>2041603105066</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <v>2041603105271</v>
+        <v>2043401357265</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1153,15 +1153,15 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>2041603105066</v>
+        <v>2042793570610</v>
       </c>
       <c r="B95">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96">
-        <v>2043401357265</v>
+        <v>2043401357197</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1169,23 +1169,23 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>2042793570610</v>
+        <v>2043401281201</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98">
-        <v>2043401357197</v>
+        <v>2043401281096</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99">
-        <v>2043401281201</v>
+        <v>2043401357234</v>
       </c>
       <c r="B99">
         <v>5</v>
@@ -1193,7 +1193,7 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>2043401281096</v>
+        <v>2043401357258</v>
       </c>
       <c r="B100">
         <v>5</v>
@@ -1201,15 +1201,15 @@
     </row>
     <row r="101">
       <c r="A101">
-        <v>2043401357234</v>
+        <v>2043401281324</v>
       </c>
       <c r="B101">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102">
-        <v>2043401357258</v>
+        <v>2043401281218</v>
       </c>
       <c r="B102">
         <v>5</v>
@@ -1217,15 +1217,15 @@
     </row>
     <row r="103">
       <c r="A103">
-        <v>2043401281324</v>
+        <v>2043401357296</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104">
-        <v>2043401281218</v>
+        <v>2043401281263</v>
       </c>
       <c r="B104">
         <v>5</v>
@@ -1233,7 +1233,7 @@
     </row>
     <row r="105">
       <c r="A105">
-        <v>2043401357296</v>
+        <v>2043401281140</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1241,15 +1241,15 @@
     </row>
     <row r="106">
       <c r="A106">
-        <v>2043401281263</v>
+        <v>2043401357210</v>
       </c>
       <c r="B106">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107">
-        <v>2043401281140</v>
+        <v>2043401281157</v>
       </c>
       <c r="B107">
         <v>5</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="108">
       <c r="A108">
-        <v>2043401357210</v>
+        <v>2043401281256</v>
       </c>
       <c r="B108">
         <v>5</v>
@@ -1265,15 +1265,15 @@
     </row>
     <row r="109">
       <c r="A109">
-        <v>2043401281157</v>
+        <v>2043401281188</v>
       </c>
       <c r="B109">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110">
-        <v>2043401281256</v>
+        <v>2047418390512</v>
       </c>
       <c r="B110">
         <v>5</v>
@@ -1281,7 +1281,7 @@
     </row>
     <row r="111">
       <c r="A111">
-        <v>2043401281188</v>
+        <v>2042793570641</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1289,7 +1289,7 @@
     </row>
     <row r="112">
       <c r="A112">
-        <v>2047418390512</v>
+        <v>2043401357203</v>
       </c>
       <c r="B112">
         <v>5</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="113">
       <c r="A113">
-        <v>2042793570641</v>
+        <v>2043401281195</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -1305,23 +1305,23 @@
     </row>
     <row r="114">
       <c r="A114">
-        <v>2043401357203</v>
+        <v>2043401281171</v>
       </c>
       <c r="B114">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115">
-        <v>2043401281195</v>
+        <v>2044222856241</v>
       </c>
       <c r="B115">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116">
-        <v>2043401281171</v>
+        <v>2043401281041</v>
       </c>
       <c r="B116">
         <v>5</v>
@@ -1329,7 +1329,7 @@
     </row>
     <row r="117">
       <c r="A117">
-        <v>2044222856241</v>
+        <v>2042793570597</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -1337,39 +1337,39 @@
     </row>
     <row r="118">
       <c r="A118">
-        <v>2043401281041</v>
+        <v>2043401281003</v>
       </c>
       <c r="B118">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119">
-        <v>2042793570597</v>
+        <v>2043401281072</v>
       </c>
       <c r="B119">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120">
       <c r="A120">
-        <v>2043401281003</v>
+        <v>2043401281089</v>
       </c>
       <c r="B120">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121">
-        <v>2043401281072</v>
+        <v>2043401281102</v>
       </c>
       <c r="B121">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122">
-        <v>2043401281089</v>
+        <v>2043401281027</v>
       </c>
       <c r="B122">
         <v>5</v>
@@ -1377,7 +1377,7 @@
     </row>
     <row r="123">
       <c r="A123">
-        <v>2043401281102</v>
+        <v>2043401281058</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -1385,23 +1385,23 @@
     </row>
     <row r="124">
       <c r="A124">
-        <v>2043401281027</v>
+        <v>2043401281133</v>
       </c>
       <c r="B124">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125">
-        <v>2043401281058</v>
+        <v>2042793570627</v>
       </c>
       <c r="B125">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126">
-        <v>2043401281133</v>
+        <v>2043401357265</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -1409,31 +1409,31 @@
     </row>
     <row r="127">
       <c r="A127">
-        <v>2042793570627</v>
+        <v>2043401281232</v>
       </c>
       <c r="B127">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128">
-        <v>2043401357265</v>
+        <v>2043401357272</v>
       </c>
       <c r="B128">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129">
-        <v>2043401281232</v>
+        <v>2043401281225</v>
       </c>
       <c r="B129">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130">
-        <v>2043401357272</v>
+        <v>2042793570634</v>
       </c>
       <c r="B130">
         <v>5</v>
@@ -1441,7 +1441,7 @@
     </row>
     <row r="131">
       <c r="A131">
-        <v>2043401281225</v>
+        <v>2042793570603</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="132">
       <c r="A132">
-        <v>2042793570634</v>
+        <v>2043401281294</v>
       </c>
       <c r="B132">
         <v>5</v>
@@ -1457,7 +1457,7 @@
     </row>
     <row r="133">
       <c r="A133">
-        <v>2042793570603</v>
+        <v>2043401357227</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -1465,55 +1465,55 @@
     </row>
     <row r="134">
       <c r="A134">
-        <v>2043401281294</v>
+        <v>2043401281249</v>
       </c>
       <c r="B134">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135">
-        <v>2043401357227</v>
+        <v>2043401281164</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136">
-        <v>2043401281249</v>
+        <v>2043401357289</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137">
-        <v>2043401281164</v>
+        <v>2043401281119</v>
       </c>
       <c r="B137">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138">
-        <v>2043401357289</v>
+        <v>2043401281126</v>
       </c>
       <c r="B138">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139">
-        <v>2043401281119</v>
+        <v>2043401281065</v>
       </c>
       <c r="B139">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140">
-        <v>2043401281126</v>
+        <v>2043401357302</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="141">
       <c r="A141">
-        <v>2043401281065</v>
+        <v>2044389037231</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -1529,7 +1529,7 @@
     </row>
     <row r="142">
       <c r="A142">
-        <v>2043401357302</v>
+        <v>2044389037255</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -1537,23 +1537,23 @@
     </row>
     <row r="143">
       <c r="A143">
-        <v>2044389037231</v>
+        <v>2041603105370</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144">
-        <v>2044389037255</v>
+        <v>2044389037347</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145">
-        <v>2041603105370</v>
+        <v>2044389037361</v>
       </c>
       <c r="B145">
         <v>5</v>
@@ -1561,23 +1561,23 @@
     </row>
     <row r="146">
       <c r="A146">
-        <v>2044389037347</v>
+        <v>2044389037385</v>
       </c>
       <c r="B146">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147">
-        <v>2044389037361</v>
+        <v>2044389037859</v>
       </c>
       <c r="B147">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148">
-        <v>2044389037385</v>
+        <v>2044389037606</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -1585,23 +1585,23 @@
     </row>
     <row r="149">
       <c r="A149">
-        <v>2044389037859</v>
+        <v>2044389037651</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150">
-        <v>2044389037606</v>
+        <v>2044389037682</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151">
-        <v>2044389037651</v>
+        <v>2044389037736</v>
       </c>
       <c r="B151">
         <v>5</v>
@@ -1609,15 +1609,15 @@
     </row>
     <row r="152">
       <c r="A152">
-        <v>2044389037682</v>
+        <v>2044389037811</v>
       </c>
       <c r="B152">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153">
-        <v>2044389037736</v>
+        <v>2044607193725</v>
       </c>
       <c r="B153">
         <v>5</v>
@@ -1625,15 +1625,15 @@
     </row>
     <row r="154">
       <c r="A154">
-        <v>2044389037811</v>
+        <v>2044607193688</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155">
-        <v>2044607193725</v>
+        <v>2044607193718</v>
       </c>
       <c r="B155">
         <v>5</v>
@@ -1641,7 +1641,7 @@
     </row>
     <row r="156">
       <c r="A156">
-        <v>2044607193688</v>
+        <v>2044607193664</v>
       </c>
       <c r="B156">
         <v>5</v>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="157">
       <c r="A157">
-        <v>2044607193718</v>
+        <v>2044607193695</v>
       </c>
       <c r="B157">
         <v>5</v>
@@ -1657,7 +1657,7 @@
     </row>
     <row r="158">
       <c r="A158">
-        <v>2044607193664</v>
+        <v>2044607193701</v>
       </c>
       <c r="B158">
         <v>5</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="159">
       <c r="A159">
-        <v>2044607193695</v>
+        <v>2045447992721</v>
       </c>
       <c r="B159">
         <v>5</v>
@@ -1673,31 +1673,31 @@
     </row>
     <row r="160">
       <c r="A160">
-        <v>2044607193701</v>
+        <v>2045447992738</v>
       </c>
       <c r="B160">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161">
-        <v>2045447992721</v>
+        <v>2045447992745</v>
       </c>
       <c r="B161">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162">
-        <v>2045447992738</v>
+        <v>2045447992752</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163">
       <c r="A163">
-        <v>2045447992745</v>
+        <v>2045447992776</v>
       </c>
       <c r="B163">
         <v>5</v>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="164">
       <c r="A164">
-        <v>2045447992752</v>
+        <v>2045447992783</v>
       </c>
       <c r="B164">
         <v>5</v>
@@ -1713,7 +1713,7 @@
     </row>
     <row r="165">
       <c r="A165">
-        <v>2045447992776</v>
+        <v>2045447992790</v>
       </c>
       <c r="B165">
         <v>5</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="166">
       <c r="A166">
-        <v>2045447992783</v>
+        <v>2045447992806</v>
       </c>
       <c r="B166">
         <v>5</v>
@@ -1729,7 +1729,7 @@
     </row>
     <row r="167">
       <c r="A167">
-        <v>2045447992790</v>
+        <v>2045447863069</v>
       </c>
       <c r="B167">
         <v>5</v>
@@ -1737,31 +1737,31 @@
     </row>
     <row r="168">
       <c r="A168">
-        <v>2045447992806</v>
+        <v>2045447863076</v>
       </c>
       <c r="B168">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169">
-        <v>2045447863069</v>
+        <v>2045447863083</v>
       </c>
       <c r="B169">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170">
-        <v>2045447863076</v>
+        <v>2045447863090</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171">
       <c r="A171">
-        <v>2045447863083</v>
+        <v>2045447863106</v>
       </c>
       <c r="B171">
         <v>5</v>
@@ -1769,7 +1769,7 @@
     </row>
     <row r="172">
       <c r="A172">
-        <v>2045447863090</v>
+        <v>2045447863113</v>
       </c>
       <c r="B172">
         <v>5</v>
@@ -1777,7 +1777,7 @@
     </row>
     <row r="173">
       <c r="A173">
-        <v>2045447863106</v>
+        <v>2045447863120</v>
       </c>
       <c r="B173">
         <v>5</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="174">
       <c r="A174">
-        <v>2045447863113</v>
+        <v>2045447863137</v>
       </c>
       <c r="B174">
         <v>5</v>
@@ -1793,7 +1793,7 @@
     </row>
     <row r="175">
       <c r="A175">
-        <v>2045447863120</v>
+        <v>2045510978966</v>
       </c>
       <c r="B175">
         <v>5</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="176">
       <c r="A176">
-        <v>2045447863137</v>
+        <v>2045510894709</v>
       </c>
       <c r="B176">
         <v>5</v>
@@ -1809,15 +1809,15 @@
     </row>
     <row r="177">
       <c r="A177">
-        <v>2045510978966</v>
+        <v>2046874095344</v>
       </c>
       <c r="B177">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178">
-        <v>2045510894709</v>
+        <v>2046874095610</v>
       </c>
       <c r="B178">
         <v>5</v>
@@ -1825,15 +1825,15 @@
     </row>
     <row r="179">
       <c r="A179">
-        <v>2046874095344</v>
+        <v>2046874095634</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180">
       <c r="A180">
-        <v>2046874095610</v>
+        <v>2046874095641</v>
       </c>
       <c r="B180">
         <v>5</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="181">
       <c r="A181">
-        <v>2046874095634</v>
+        <v>2046874457357</v>
       </c>
       <c r="B181">
         <v>5</v>
@@ -1849,7 +1849,7 @@
     </row>
     <row r="182">
       <c r="A182">
-        <v>2046874095641</v>
+        <v>2046874457401</v>
       </c>
       <c r="B182">
         <v>5</v>
@@ -1857,15 +1857,15 @@
     </row>
     <row r="183">
       <c r="A183">
-        <v>2046874457357</v>
+        <v>2046874457340</v>
       </c>
       <c r="B183">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184">
-        <v>2046874457401</v>
+        <v>2046874457395</v>
       </c>
       <c r="B184">
         <v>5</v>
@@ -1873,7 +1873,7 @@
     </row>
     <row r="185">
       <c r="A185">
-        <v>2046874457340</v>
+        <v>2047404870929</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -1881,7 +1881,7 @@
     </row>
     <row r="186">
       <c r="A186">
-        <v>2046874457395</v>
+        <v>2047404870936</v>
       </c>
       <c r="B186">
         <v>5</v>
@@ -1889,15 +1889,15 @@
     </row>
     <row r="187">
       <c r="A187">
-        <v>2047404870929</v>
+        <v>2047404870974</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188">
       <c r="A188">
-        <v>2047404870936</v>
+        <v>2047396898048</v>
       </c>
       <c r="B188">
         <v>5</v>
@@ -1905,7 +1905,7 @@
     </row>
     <row r="189">
       <c r="A189">
-        <v>2047404870974</v>
+        <v>2047396898017</v>
       </c>
       <c r="B189">
         <v>5</v>
@@ -1913,31 +1913,31 @@
     </row>
     <row r="190">
       <c r="A190">
-        <v>2047396898048</v>
+        <v>2047396898079</v>
       </c>
       <c r="B190">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
       <c r="A191">
-        <v>2047396898017</v>
+        <v>2048856638334</v>
       </c>
       <c r="B191">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
       <c r="A192">
-        <v>2047396898079</v>
+        <v>2048856638303</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193">
       <c r="A193">
-        <v>2048856638334</v>
+        <v>2048856638310</v>
       </c>
       <c r="B193">
         <v>5</v>
@@ -1945,23 +1945,23 @@
     </row>
     <row r="194">
       <c r="A194">
-        <v>2048856638303</v>
+        <v>2048856638389</v>
       </c>
       <c r="B194">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
       <c r="A195">
-        <v>2048856638310</v>
+        <v>2048856638365</v>
       </c>
       <c r="B195">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
       <c r="A196">
-        <v>2048856638389</v>
+        <v>2048856638358</v>
       </c>
       <c r="B196">
         <v>5</v>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="197">
       <c r="A197">
-        <v>2048856638365</v>
+        <v>2048856638372</v>
       </c>
       <c r="B197">
         <v>5</v>
@@ -1977,31 +1977,15 @@
     </row>
     <row r="198">
       <c r="A198">
-        <v>2048856638358</v>
+        <v>2048856638341</v>
       </c>
       <c r="B198">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199">
-        <v>2048856638372</v>
-      </c>
-      <c r="B199">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200">
-        <v>2048856638341</v>
-      </c>
-      <c r="B200">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B198"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/ready_stocks/galtex-wb-stocks-updated.xlsx
+++ b/data/ready_stocks/galtex-wb-stocks-updated.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B198"/>
+  <dimension ref="A1:B152"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -408,64 +408,64 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>2041603105134</v>
+      <c r="A2">
+        <v>2044249667004</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>2041603105158</v>
+      <c r="A3">
+        <v>2044249667011</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>2041603105387</v>
+      <c r="A4">
+        <v>2044249667028</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>2041603105394</v>
+      <c r="A5">
+        <v>2044249667035</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>2041603105400</v>
+      <c r="A6">
+        <v>2044249667059</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>2041603105417</v>
+      <c r="A7">
+        <v>2044249667073</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>2041603105424</v>
+      <c r="A8">
+        <v>2044249667097</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>2041603105431</v>
+      <c r="A9">
+        <v>2044249667103</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -473,119 +473,119 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>2044186087804</v>
+        <v>2044249667127</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>2041603105455</v>
+      <c r="A11">
+        <v>2044249667240</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>2041603105462</v>
+      <c r="A12">
+        <v>2044249667257</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v>2041603105479</v>
+      <c r="A13">
+        <v>2044249667271</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>2041603105486</v>
+      <c r="A14">
+        <v>2044249667288</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>2041603105493</v>
+      <c r="A15">
+        <v>2044249667318</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
-        <v>2041603105509</v>
+      <c r="A16">
+        <v>2044249667325</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
-        <v>2041602656262</v>
+      <c r="A17">
+        <v>2044249667349</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
-        <v>2042234857515</v>
+      <c r="A18">
+        <v>2044249667417</v>
       </c>
       <c r="B18">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
-        <v>2042234857522</v>
+      <c r="A19">
+        <v>2044249667431</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="str">
-        <v>2042675781165</v>
+      <c r="A20">
+        <v>2044249667448</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
-        <v>2042234857416</v>
+      <c r="A21">
+        <v>2044249667486</v>
       </c>
       <c r="B21">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="str">
-        <v>2042234857423</v>
+      <c r="A22">
+        <v>2044249667493</v>
       </c>
       <c r="B22">
         <v>5</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
-        <v>2042234857492</v>
+      <c r="A23">
+        <v>2044249667530</v>
       </c>
       <c r="B23">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>2044186087811</v>
+        <v>2044249667547</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -593,527 +593,527 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>2044186087828</v>
+        <v>2044249667554</v>
       </c>
       <c r="B25">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
-        <v>2043366775043</v>
+      <c r="A26">
+        <v>2044249667561</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str">
-        <v>2043792548891</v>
+      <c r="A27">
+        <v>2044249667578</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str">
-        <v>2043792548907</v>
+      <c r="A28">
+        <v>2044249667585</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str">
-        <v>2043792548860</v>
+      <c r="A29">
+        <v>2044249667592</v>
       </c>
       <c r="B29">
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="str">
-        <v>2043792548938</v>
+      <c r="A30">
+        <v>2044249667806</v>
       </c>
       <c r="B30">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="str">
-        <v>2043792548877</v>
+      <c r="A31">
+        <v>2044249667813</v>
       </c>
       <c r="B31">
         <v>5</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="str">
-        <v>2043792548921</v>
+      <c r="A32">
+        <v>2044249667820</v>
       </c>
       <c r="B32">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str">
-        <v>2041603105080</v>
+      <c r="A33">
+        <v>2044249667837</v>
       </c>
       <c r="B33">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
-        <v>2041603105127</v>
+      <c r="A34">
+        <v>2044249667868</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
-        <v>2041603105516</v>
+      <c r="A35">
+        <v>2044249667967</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
-        <v>2041603105523</v>
+      <c r="A36">
+        <v>2044249667974</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
-        <v>2041603105530</v>
+      <c r="A37">
+        <v>2044249667981</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
-        <v>2041603105547</v>
+      <c r="A38">
+        <v>2044249667998</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str">
-        <v>2041603105554</v>
+      <c r="A39">
+        <v>2044249668001</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str">
-        <v>2041603105561</v>
+      <c r="A40">
+        <v>2044249668650</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="str">
-        <v>2041603105578</v>
+      <c r="A41">
+        <v>2044249668667</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="str">
-        <v>2042234857485</v>
+      <c r="A42">
+        <v>2044249668674</v>
       </c>
       <c r="B42">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="str">
-        <v>2042234857430</v>
+      <c r="A43">
+        <v>2044249668773</v>
       </c>
       <c r="B43">
         <v>5</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="str">
-        <v>2042675781066</v>
+      <c r="A44">
+        <v>2044249668889</v>
       </c>
       <c r="B44">
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="str">
-        <v>2042675781073</v>
+      <c r="A45">
+        <v>2044249668896</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="str">
-        <v>2042675781080</v>
+      <c r="A46">
+        <v>2044249668902</v>
       </c>
       <c r="B46">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="str">
-        <v>2042675781097</v>
+      <c r="A47">
+        <v>2044249668919</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="str">
-        <v>2042675781103</v>
+      <c r="A48">
+        <v>2044249669022</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="str">
-        <v>2042675781110</v>
+      <c r="A49">
+        <v>2044249669046</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="str">
-        <v>2042675781127</v>
+      <c r="A50">
+        <v>2044249669275</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="str">
-        <v>2042234857546</v>
+      <c r="A51">
+        <v>2044249669282</v>
       </c>
       <c r="B51">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="str">
-        <v>2042234857454</v>
+      <c r="A52">
+        <v>2044249669299</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="str">
-        <v>2042675781141</v>
+      <c r="A53">
+        <v>2044249669305</v>
       </c>
       <c r="B53">
         <v>5</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="str">
-        <v>2042280034557</v>
+      <c r="A54">
+        <v>2044249669312</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>2044186087835</v>
+        <v>2044249669329</v>
       </c>
       <c r="B55">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>2044186087842</v>
+        <v>2044249669336</v>
       </c>
       <c r="B56">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="str">
-        <v>2043366775104</v>
+      <c r="A57">
+        <v>2044249669343</v>
       </c>
       <c r="B57">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="str">
-        <v>2043366775050</v>
+      <c r="A58">
+        <v>2044249669350</v>
       </c>
       <c r="B58">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="str">
-        <v>2043366775067</v>
+      <c r="A59">
+        <v>2044249669367</v>
       </c>
       <c r="B59">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="str">
-        <v>2043366775074</v>
+      <c r="A60">
+        <v>2044249669398</v>
       </c>
       <c r="B60">
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="str">
-        <v>2043366775081</v>
+      <c r="A61">
+        <v>2044249669404</v>
       </c>
       <c r="B61">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="str">
-        <v>2043366775098</v>
+      <c r="A62">
+        <v>2044249669428</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="str">
-        <v>2041603105097</v>
+      <c r="A63">
+        <v>2044249669435</v>
       </c>
       <c r="B63">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="str">
-        <v>2041603105141</v>
+      <c r="A64">
+        <v>2044249669442</v>
       </c>
       <c r="B64">
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="str">
-        <v>2041603105165</v>
+      <c r="A65">
+        <v>2044249669541</v>
       </c>
       <c r="B65">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="str">
-        <v>2041603105189</v>
+      <c r="A66">
+        <v>2044249669558</v>
       </c>
       <c r="B66">
         <v>5</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="str">
-        <v>2041603105202</v>
+      <c r="A67">
+        <v>2044607028577</v>
       </c>
       <c r="B67">
         <v>5</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="str">
-        <v>2041603105226</v>
+      <c r="A68">
+        <v>2044607028621</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="str">
-        <v>2041603105233</v>
+      <c r="A69">
+        <v>2044607028607</v>
       </c>
       <c r="B69">
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="str">
-        <v>2041603105240</v>
+      <c r="A70">
+        <v>2044607028638</v>
       </c>
       <c r="B70">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="str">
-        <v>2041603105257</v>
+      <c r="A71">
+        <v>2044607028614</v>
       </c>
       <c r="B71">
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="str">
-        <v>2041603105264</v>
+      <c r="A72">
+        <v>2044607028584</v>
       </c>
       <c r="B72">
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="str">
-        <v>2041603105288</v>
+      <c r="A73">
+        <v>2044607028591</v>
       </c>
       <c r="B73">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="str">
-        <v>2041603105295</v>
+      <c r="A74">
+        <v>2044607028560</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="str">
-        <v>2041603105318</v>
+      <c r="A75">
+        <v>2044607028546</v>
       </c>
       <c r="B75">
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="str">
-        <v>2041603105325</v>
+      <c r="A76">
+        <v>2044607028553</v>
       </c>
       <c r="B76">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="str">
-        <v>2041603105332</v>
+      <c r="A77">
+        <v>2044607028423</v>
       </c>
       <c r="B77">
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="str">
-        <v>2041603105349</v>
+      <c r="A78">
+        <v>2044607028492</v>
       </c>
       <c r="B78">
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="str">
-        <v>2041603105363</v>
+      <c r="A79">
+        <v>2044607028430</v>
       </c>
       <c r="B79">
         <v>5</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="str">
-        <v>2041603105585</v>
+      <c r="A80">
+        <v>2044607028454</v>
       </c>
       <c r="B80">
         <v>5</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="str">
-        <v>2042675781172</v>
+      <c r="A81">
+        <v>2044607028379</v>
       </c>
       <c r="B81">
         <v>5</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="str">
-        <v>2042675781189</v>
+      <c r="A82">
+        <v>2044607028362</v>
       </c>
       <c r="B82">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="str">
-        <v>2042675781196</v>
+      <c r="A83">
+        <v>2044607028515</v>
       </c>
       <c r="B83">
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="str">
-        <v>2042675781202</v>
+      <c r="A84">
+        <v>2044607028508</v>
       </c>
       <c r="B84">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="str">
-        <v>2042675781219</v>
+      <c r="A85">
+        <v>2044607028461</v>
       </c>
       <c r="B85">
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="str">
-        <v>2042675781226</v>
+      <c r="A86">
+        <v>2044607028447</v>
       </c>
       <c r="B86">
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="str">
-        <v>2042675781233</v>
+      <c r="A87">
+        <v>2044607028386</v>
       </c>
       <c r="B87">
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="str">
-        <v>2042675781240</v>
+      <c r="A88">
+        <v>2044607028522</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="str">
-        <v>2042675781257</v>
+      <c r="A89">
+        <v>2044607028485</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="str">
-        <v>2042675781264</v>
+      <c r="A90">
+        <v>2044607028393</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1121,7 +1121,7 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>2041603105301</v>
+        <v>2044607028348</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1129,15 +1129,15 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>2041603105271</v>
+        <v>2044607028478</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <v>2041603105066</v>
+        <v>2044607028409</v>
       </c>
       <c r="B93">
         <v>5</v>
@@ -1145,7 +1145,7 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>2043401357265</v>
+        <v>2044607028355</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1153,15 +1153,15 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>2042793570610</v>
+        <v>2044607028416</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96">
-        <v>2043401357197</v>
+        <v>2045448714698</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1169,15 +1169,15 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>2043401281201</v>
+        <v>2046874026553</v>
       </c>
       <c r="B97">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98">
-        <v>2043401281096</v>
+        <v>2046874026584</v>
       </c>
       <c r="B98">
         <v>5</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>2043401357234</v>
+        <v>2046874026607</v>
       </c>
       <c r="B99">
         <v>5</v>
@@ -1193,15 +1193,15 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>2043401357258</v>
+        <v>2046874026614</v>
       </c>
       <c r="B100">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101">
-        <v>2043401281324</v>
+        <v>2046874026621</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1209,15 +1209,15 @@
     </row>
     <row r="102">
       <c r="A102">
-        <v>2043401281218</v>
+        <v>2046874026645</v>
       </c>
       <c r="B102">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103">
-        <v>2043401357296</v>
+        <v>2046874026669</v>
       </c>
       <c r="B103">
         <v>5</v>
@@ -1225,15 +1225,15 @@
     </row>
     <row r="104">
       <c r="A104">
-        <v>2043401281263</v>
+        <v>2046874026676</v>
       </c>
       <c r="B104">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105">
-        <v>2043401281140</v>
+        <v>2046874026683</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     </row>
     <row r="106">
       <c r="A106">
-        <v>2043401357210</v>
+        <v>2046874026706</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1249,23 +1249,23 @@
     </row>
     <row r="107">
       <c r="A107">
-        <v>2043401281157</v>
+        <v>2046874026720</v>
       </c>
       <c r="B107">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108">
-        <v>2043401281256</v>
+        <v>2046874026751</v>
       </c>
       <c r="B108">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109">
-        <v>2043401281188</v>
+        <v>2046874026775</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1273,15 +1273,15 @@
     </row>
     <row r="110">
       <c r="A110">
-        <v>2047418390512</v>
+        <v>2046874026799</v>
       </c>
       <c r="B110">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111">
-        <v>2042793570641</v>
+        <v>2046874026812</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1289,7 +1289,7 @@
     </row>
     <row r="112">
       <c r="A112">
-        <v>2043401357203</v>
+        <v>2046874026829</v>
       </c>
       <c r="B112">
         <v>5</v>
@@ -1297,15 +1297,15 @@
     </row>
     <row r="113">
       <c r="A113">
-        <v>2043401281195</v>
+        <v>2046874026843</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114">
       <c r="A114">
-        <v>2043401281171</v>
+        <v>2046874026850</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="115">
       <c r="A115">
-        <v>2044222856241</v>
+        <v>2047397367826</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -1321,7 +1321,7 @@
     </row>
     <row r="116">
       <c r="A116">
-        <v>2043401281041</v>
+        <v>2047397367796</v>
       </c>
       <c r="B116">
         <v>5</v>
@@ -1329,7 +1329,7 @@
     </row>
     <row r="117">
       <c r="A117">
-        <v>2042793570597</v>
+        <v>2047397367789</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -1337,15 +1337,15 @@
     </row>
     <row r="118">
       <c r="A118">
-        <v>2043401281003</v>
+        <v>2048854039775</v>
       </c>
       <c r="B118">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
       <c r="A119">
-        <v>2043401281072</v>
+        <v>2048854039805</v>
       </c>
       <c r="B119">
         <v>5</v>
@@ -1353,7 +1353,7 @@
     </row>
     <row r="120">
       <c r="A120">
-        <v>2043401281089</v>
+        <v>2048854039881</v>
       </c>
       <c r="B120">
         <v>5</v>
@@ -1361,31 +1361,31 @@
     </row>
     <row r="121">
       <c r="A121">
-        <v>2043401281102</v>
+        <v>2048854039904</v>
       </c>
       <c r="B121">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122">
-        <v>2043401281027</v>
+        <v>2048854039973</v>
       </c>
       <c r="B122">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123">
-        <v>2043401281058</v>
+        <v>2048854040016</v>
       </c>
       <c r="B123">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124">
-        <v>2043401281133</v>
+        <v>2048854039911</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -1393,7 +1393,7 @@
     </row>
     <row r="125">
       <c r="A125">
-        <v>2042793570627</v>
+        <v>2048854040023</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -1401,7 +1401,7 @@
     </row>
     <row r="126">
       <c r="A126">
-        <v>2043401357265</v>
+        <v>2048854039935</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="127">
       <c r="A127">
-        <v>2043401281232</v>
+        <v>2048854040054</v>
       </c>
       <c r="B127">
         <v>5</v>
@@ -1417,15 +1417,15 @@
     </row>
     <row r="128">
       <c r="A128">
-        <v>2043401357272</v>
+        <v>2048854039966</v>
       </c>
       <c r="B128">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129">
-        <v>2043401281225</v>
+        <v>2048854040047</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -1433,31 +1433,31 @@
     </row>
     <row r="130">
       <c r="A130">
-        <v>2042793570634</v>
+        <v>2048854039980</v>
       </c>
       <c r="B130">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131">
-        <v>2042793570603</v>
+        <v>2048854039959</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132">
-        <v>2043401281294</v>
+        <v>2048854039867</v>
       </c>
       <c r="B132">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133">
-        <v>2043401357227</v>
+        <v>2048854039898</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -1465,31 +1465,31 @@
     </row>
     <row r="134">
       <c r="A134">
-        <v>2043401281249</v>
+        <v>2048854040030</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135">
       <c r="A135">
-        <v>2043401281164</v>
+        <v>2048854039843</v>
       </c>
       <c r="B135">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136">
-        <v>2043401357289</v>
+        <v>2048854039942</v>
       </c>
       <c r="B136">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137">
-        <v>2043401281119</v>
+        <v>2048854039874</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -1497,15 +1497,15 @@
     </row>
     <row r="138">
       <c r="A138">
-        <v>2043401281126</v>
+        <v>2048854040009</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139">
-        <v>2043401281065</v>
+        <v>2050458499541</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -1513,7 +1513,7 @@
     </row>
     <row r="140">
       <c r="A140">
-        <v>2043401357302</v>
+        <v>2050458500209</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="141">
       <c r="A141">
-        <v>2044389037231</v>
+        <v>2050458499572</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -1529,55 +1529,55 @@
     </row>
     <row r="142">
       <c r="A142">
-        <v>2044389037255</v>
+        <v>2050458499916</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143">
-        <v>2041603105370</v>
+        <v>2050458499626</v>
       </c>
       <c r="B143">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144">
-        <v>2044389037347</v>
+        <v>2050458500094</v>
       </c>
       <c r="B144">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145">
-        <v>2044389037361</v>
+        <v>2050458499992</v>
       </c>
       <c r="B145">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146">
-        <v>2044389037385</v>
+        <v>2050458500186</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147">
-        <v>2044389037859</v>
+        <v>2050458499824</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148">
-        <v>2044389037606</v>
+        <v>2050458499596</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="149">
       <c r="A149">
-        <v>2044389037651</v>
+        <v>2050458499435</v>
       </c>
       <c r="B149">
         <v>5</v>
@@ -1593,15 +1593,15 @@
     </row>
     <row r="150">
       <c r="A150">
-        <v>2044389037682</v>
+        <v>2050458499787</v>
       </c>
       <c r="B150">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151">
-        <v>2044389037736</v>
+        <v>2050458500308</v>
       </c>
       <c r="B151">
         <v>5</v>
@@ -1609,383 +1609,15 @@
     </row>
     <row r="152">
       <c r="A152">
-        <v>2044389037811</v>
+        <v>2050458500049</v>
       </c>
       <c r="B152">
         <v>0</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153">
-        <v>2044607193725</v>
-      </c>
-      <c r="B153">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154">
-        <v>2044607193688</v>
-      </c>
-      <c r="B154">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155">
-        <v>2044607193718</v>
-      </c>
-      <c r="B155">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156">
-        <v>2044607193664</v>
-      </c>
-      <c r="B156">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157">
-        <v>2044607193695</v>
-      </c>
-      <c r="B157">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158">
-        <v>2044607193701</v>
-      </c>
-      <c r="B158">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159">
-        <v>2045447992721</v>
-      </c>
-      <c r="B159">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160">
-        <v>2045447992738</v>
-      </c>
-      <c r="B160">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161">
-        <v>2045447992745</v>
-      </c>
-      <c r="B161">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162">
-        <v>2045447992752</v>
-      </c>
-      <c r="B162">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163">
-        <v>2045447992776</v>
-      </c>
-      <c r="B163">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164">
-        <v>2045447992783</v>
-      </c>
-      <c r="B164">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165">
-        <v>2045447992790</v>
-      </c>
-      <c r="B165">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166">
-        <v>2045447992806</v>
-      </c>
-      <c r="B166">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167">
-        <v>2045447863069</v>
-      </c>
-      <c r="B167">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168">
-        <v>2045447863076</v>
-      </c>
-      <c r="B168">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169">
-        <v>2045447863083</v>
-      </c>
-      <c r="B169">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170">
-        <v>2045447863090</v>
-      </c>
-      <c r="B170">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171">
-        <v>2045447863106</v>
-      </c>
-      <c r="B171">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172">
-        <v>2045447863113</v>
-      </c>
-      <c r="B172">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173">
-        <v>2045447863120</v>
-      </c>
-      <c r="B173">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174">
-        <v>2045447863137</v>
-      </c>
-      <c r="B174">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175">
-        <v>2045510978966</v>
-      </c>
-      <c r="B175">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176">
-        <v>2045510894709</v>
-      </c>
-      <c r="B176">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177">
-        <v>2046874095344</v>
-      </c>
-      <c r="B177">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178">
-        <v>2046874095610</v>
-      </c>
-      <c r="B178">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179">
-        <v>2046874095634</v>
-      </c>
-      <c r="B179">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180">
-        <v>2046874095641</v>
-      </c>
-      <c r="B180">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181">
-        <v>2046874457357</v>
-      </c>
-      <c r="B181">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182">
-        <v>2046874457401</v>
-      </c>
-      <c r="B182">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183">
-        <v>2046874457340</v>
-      </c>
-      <c r="B183">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184">
-        <v>2046874457395</v>
-      </c>
-      <c r="B184">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185">
-        <v>2047404870929</v>
-      </c>
-      <c r="B185">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186">
-        <v>2047404870936</v>
-      </c>
-      <c r="B186">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187">
-        <v>2047404870974</v>
-      </c>
-      <c r="B187">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188">
-        <v>2047396898048</v>
-      </c>
-      <c r="B188">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189">
-        <v>2047396898017</v>
-      </c>
-      <c r="B189">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190">
-        <v>2047396898079</v>
-      </c>
-      <c r="B190">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191">
-        <v>2048856638334</v>
-      </c>
-      <c r="B191">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192">
-        <v>2048856638303</v>
-      </c>
-      <c r="B192">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193">
-        <v>2048856638310</v>
-      </c>
-      <c r="B193">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194">
-        <v>2048856638389</v>
-      </c>
-      <c r="B194">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195">
-        <v>2048856638365</v>
-      </c>
-      <c r="B195">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196">
-        <v>2048856638358</v>
-      </c>
-      <c r="B196">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197">
-        <v>2048856638372</v>
-      </c>
-      <c r="B197">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198">
-        <v>2048856638341</v>
-      </c>
-      <c r="B198">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B198"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B152"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/ready_stocks/galtex-wb-stocks-updated.xlsx
+++ b/data/ready_stocks/galtex-wb-stocks-updated.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B152"/>
+  <dimension ref="A1:B154"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -409,15 +409,15 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>2044249667004</v>
+        <v>2044249666984</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>2044249667011</v>
+        <v>2044249667004</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -425,7 +425,7 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>2044249667028</v>
+        <v>2044249667011</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -433,7 +433,7 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>2044249667035</v>
+        <v>2044249667028</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -441,7 +441,7 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>2044249667059</v>
+        <v>2044249667035</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -449,7 +449,7 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>2044249667073</v>
+        <v>2044249667059</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -457,7 +457,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>2044249667097</v>
+        <v>2044249667073</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -465,23 +465,23 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>2044249667103</v>
+        <v>2044249667097</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>2044249667127</v>
+        <v>2044249667103</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>2044249667240</v>
+        <v>2044249667127</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -489,7 +489,7 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>2044249667257</v>
+        <v>2044249667240</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -497,23 +497,23 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>2044249667271</v>
+        <v>2044249667257</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>2044249667288</v>
+        <v>2044249667271</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>2044249667318</v>
+        <v>2044249667288</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -521,7 +521,7 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>2044249667325</v>
+        <v>2044249667318</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -529,7 +529,7 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>2044249667349</v>
+        <v>2044249667325</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -537,7 +537,7 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>2044249667417</v>
+        <v>2044249667349</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -545,7 +545,7 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>2044249667431</v>
+        <v>2044249667417</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -553,7 +553,7 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>2044249667448</v>
+        <v>2044249667431</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -561,7 +561,7 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>2044249667486</v>
+        <v>2044249667448</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -569,23 +569,23 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>2044249667493</v>
+        <v>2044249667486</v>
       </c>
       <c r="B22">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>2044249667530</v>
+        <v>2044249667493</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>2044249667547</v>
+        <v>2044249667530</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -593,7 +593,7 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>2044249667554</v>
+        <v>2044249667547</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -601,7 +601,7 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>2044249667561</v>
+        <v>2044249667554</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>2044249667578</v>
+        <v>2044249667561</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -617,23 +617,23 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>2044249667585</v>
+        <v>2044249667578</v>
       </c>
       <c r="B28">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>2044249667592</v>
+        <v>2044249667585</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>2044249667806</v>
+        <v>2044249667592</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -641,23 +641,23 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>2044249667813</v>
+        <v>2044249667806</v>
       </c>
       <c r="B31">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>2044249667820</v>
+        <v>2044249667813</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>2044249667837</v>
+        <v>2044249667820</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -665,7 +665,7 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>2044249667868</v>
+        <v>2044249667837</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -673,7 +673,7 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>2044249667967</v>
+        <v>2044249667868</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -681,7 +681,7 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>2044249667974</v>
+        <v>2044249667967</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -689,39 +689,39 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>2044249667981</v>
+        <v>2044249667974</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>2044249667998</v>
+        <v>2044249667981</v>
       </c>
       <c r="B38">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>2044249668001</v>
+        <v>2044249667998</v>
       </c>
       <c r="B39">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>2044249668650</v>
+        <v>2044249668001</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>2044249668667</v>
+        <v>2044249668650</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -729,7 +729,7 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>2044249668674</v>
+        <v>2044249668667</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -737,23 +737,23 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>2044249668773</v>
+        <v>2044249668674</v>
       </c>
       <c r="B43">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>2044249668889</v>
+        <v>2044249668773</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>2044249668896</v>
+        <v>2044249668889</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -761,7 +761,7 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>2044249668902</v>
+        <v>2044249668896</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -769,7 +769,7 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>2044249668919</v>
+        <v>2044249668902</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -777,71 +777,71 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>2044249669022</v>
+        <v>2044249668919</v>
       </c>
       <c r="B48">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>2044249669046</v>
+        <v>2044249669022</v>
       </c>
       <c r="B49">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>2044249669275</v>
+        <v>2044249669046</v>
       </c>
       <c r="B50">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>2044249669282</v>
+        <v>2044249669275</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>2044249669299</v>
+        <v>2044249669282</v>
       </c>
       <c r="B52">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>2044249669305</v>
+        <v>2044249669299</v>
       </c>
       <c r="B53">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>2044249669312</v>
+        <v>2044249669305</v>
       </c>
       <c r="B54">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>2044249669329</v>
+        <v>2044249669312</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>2044249669336</v>
+        <v>2044249669329</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -849,7 +849,7 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>2044249669343</v>
+        <v>2044249669336</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -857,15 +857,15 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>2044249669350</v>
+        <v>2044249669343</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>2044249669367</v>
+        <v>2044249669350</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -873,7 +873,7 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>2044249669398</v>
+        <v>2044249669367</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -881,7 +881,7 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>2044249669404</v>
+        <v>2044249669398</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>2044249669428</v>
+        <v>2044249669404</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>2044249669435</v>
+        <v>2044249669428</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>2044249669442</v>
+        <v>2044249669435</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -913,7 +913,7 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>2044249669541</v>
+        <v>2044249669442</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -921,39 +921,39 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>2044249669558</v>
+        <v>2044249669541</v>
       </c>
       <c r="B66">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <v>2044607028577</v>
+        <v>2044249669558</v>
       </c>
       <c r="B67">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>2044607028621</v>
+        <v>2044607028577</v>
       </c>
       <c r="B68">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69">
       <c r="A69">
-        <v>2044607028607</v>
+        <v>2044607028621</v>
       </c>
       <c r="B69">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>2044607028638</v>
+        <v>2044607028607</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -961,7 +961,7 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>2044607028614</v>
+        <v>2044607028638</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -969,7 +969,7 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>2044607028584</v>
+        <v>2044607028614</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -977,7 +977,7 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>2044607028591</v>
+        <v>2044607028584</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -985,23 +985,23 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>2044607028560</v>
+        <v>2044607028591</v>
       </c>
       <c r="B74">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>2044607028546</v>
+        <v>2044607028560</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>2044607028553</v>
+        <v>2044607028546</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>2044607028423</v>
+        <v>2044607028553</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>2044607028492</v>
+        <v>2044607028423</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1025,39 +1025,39 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>2044607028430</v>
+        <v>2044607028492</v>
       </c>
       <c r="B79">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <v>2044607028454</v>
+        <v>2044607028430</v>
       </c>
       <c r="B80">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <v>2044607028379</v>
+        <v>2044607028454</v>
       </c>
       <c r="B81">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82">
       <c r="A82">
-        <v>2044607028362</v>
+        <v>2044607028379</v>
       </c>
       <c r="B82">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
       <c r="A83">
-        <v>2044607028515</v>
+        <v>2044607028362</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1065,7 +1065,7 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>2044607028508</v>
+        <v>2044607028515</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>2044607028461</v>
+        <v>2044607028508</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>2044607028447</v>
+        <v>2044607028461</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1089,7 +1089,7 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>2044607028386</v>
+        <v>2044607028447</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1097,31 +1097,31 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>2044607028522</v>
+        <v>2044607028386</v>
       </c>
       <c r="B88">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <v>2044607028485</v>
+        <v>2044607028522</v>
       </c>
       <c r="B89">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90">
       <c r="A90">
-        <v>2044607028393</v>
+        <v>2044607028485</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91">
       <c r="A91">
-        <v>2044607028348</v>
+        <v>2044607028393</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1129,47 +1129,47 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>2044607028478</v>
+        <v>2044607028348</v>
       </c>
       <c r="B92">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <v>2044607028409</v>
+        <v>2044607028478</v>
       </c>
       <c r="B93">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <v>2044607028355</v>
+        <v>2044607028409</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95">
       <c r="A95">
-        <v>2044607028416</v>
+        <v>2044607028355</v>
       </c>
       <c r="B95">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96">
-        <v>2045448714698</v>
+        <v>2044607028416</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97">
       <c r="A97">
-        <v>2046874026553</v>
+        <v>2045448714698</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -1177,31 +1177,31 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>2046874026584</v>
+        <v>2046874026553</v>
       </c>
       <c r="B98">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99">
-        <v>2046874026607</v>
+        <v>2046874026584</v>
       </c>
       <c r="B99">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="100">
       <c r="A100">
-        <v>2046874026614</v>
+        <v>2046874026607</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101">
       <c r="A101">
-        <v>2046874026621</v>
+        <v>2046874026614</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="102">
       <c r="A102">
-        <v>2046874026645</v>
+        <v>2046874026621</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1217,23 +1217,23 @@
     </row>
     <row r="103">
       <c r="A103">
-        <v>2046874026669</v>
+        <v>2046874026645</v>
       </c>
       <c r="B103">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104">
-        <v>2046874026676</v>
+        <v>2046874026669</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="105">
       <c r="A105">
-        <v>2046874026683</v>
+        <v>2046874026676</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1241,15 +1241,15 @@
     </row>
     <row r="106">
       <c r="A106">
-        <v>2046874026706</v>
+        <v>2046874026683</v>
       </c>
       <c r="B106">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="107">
       <c r="A107">
-        <v>2046874026720</v>
+        <v>2046874026706</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="108">
       <c r="A108">
-        <v>2046874026751</v>
+        <v>2046874026720</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1265,7 +1265,7 @@
     </row>
     <row r="109">
       <c r="A109">
-        <v>2046874026775</v>
+        <v>2046874026751</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     </row>
     <row r="110">
       <c r="A110">
-        <v>2046874026799</v>
+        <v>2046874026775</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -1281,7 +1281,7 @@
     </row>
     <row r="111">
       <c r="A111">
-        <v>2046874026812</v>
+        <v>2046874026799</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1289,111 +1289,111 @@
     </row>
     <row r="112">
       <c r="A112">
-        <v>2046874026829</v>
+        <v>2046874026812</v>
       </c>
       <c r="B112">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113">
-        <v>2046874026843</v>
+        <v>2046874026829</v>
       </c>
       <c r="B113">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="114">
       <c r="A114">
-        <v>2046874026850</v>
+        <v>2046874026843</v>
       </c>
       <c r="B114">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="115">
       <c r="A115">
-        <v>2047397367826</v>
+        <v>2046874026850</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="116">
       <c r="A116">
-        <v>2047397367796</v>
+        <v>2047397367826</v>
       </c>
       <c r="B116">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117">
-        <v>2047397367789</v>
+        <v>2047397367796</v>
       </c>
       <c r="B117">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="118">
       <c r="A118">
-        <v>2048854039775</v>
+        <v>2047397367789</v>
       </c>
       <c r="B118">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119">
-        <v>2048854039805</v>
+        <v>2048854039775</v>
       </c>
       <c r="B119">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="120">
       <c r="A120">
-        <v>2048854039881</v>
+        <v>2048854039805</v>
       </c>
       <c r="B120">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="121">
       <c r="A121">
-        <v>2048854039904</v>
+        <v>2048854039881</v>
       </c>
       <c r="B121">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="122">
       <c r="A122">
-        <v>2048854039973</v>
+        <v>2048854039904</v>
       </c>
       <c r="B122">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="123">
       <c r="A123">
-        <v>2048854040016</v>
+        <v>2048854039973</v>
       </c>
       <c r="B123">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="124">
       <c r="A124">
-        <v>2048854039911</v>
+        <v>2048854040016</v>
       </c>
       <c r="B124">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="125">
       <c r="A125">
-        <v>2048854040023</v>
+        <v>2048854039911</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -1401,7 +1401,7 @@
     </row>
     <row r="126">
       <c r="A126">
-        <v>2048854039935</v>
+        <v>2048854040023</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -1409,23 +1409,23 @@
     </row>
     <row r="127">
       <c r="A127">
-        <v>2048854040054</v>
+        <v>2048854039935</v>
       </c>
       <c r="B127">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128">
-        <v>2048854039966</v>
+        <v>2048854040054</v>
       </c>
       <c r="B128">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129">
       <c r="A129">
-        <v>2048854040047</v>
+        <v>2048854039966</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="130">
       <c r="A130">
-        <v>2048854039980</v>
+        <v>2048854040047</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -1441,23 +1441,23 @@
     </row>
     <row r="131">
       <c r="A131">
-        <v>2048854039959</v>
+        <v>2048854039980</v>
       </c>
       <c r="B131">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="132">
       <c r="A132">
-        <v>2048854039867</v>
+        <v>2048854039959</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="133">
       <c r="A133">
-        <v>2048854039898</v>
+        <v>2048854039867</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -1465,23 +1465,23 @@
     </row>
     <row r="134">
       <c r="A134">
-        <v>2048854040030</v>
+        <v>2048854039898</v>
       </c>
       <c r="B134">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135">
       <c r="A135">
-        <v>2048854039843</v>
+        <v>2048854040030</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="136">
       <c r="A136">
-        <v>2048854039942</v>
+        <v>2048854039843</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -1489,31 +1489,31 @@
     </row>
     <row r="137">
       <c r="A137">
-        <v>2048854039874</v>
+        <v>2048854039942</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="138">
       <c r="A138">
-        <v>2048854040009</v>
+        <v>2048854039874</v>
       </c>
       <c r="B138">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139">
       <c r="A139">
-        <v>2050458499541</v>
+        <v>2048854040009</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="140">
       <c r="A140">
-        <v>2050458500209</v>
+        <v>2050458499541</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -1521,31 +1521,31 @@
     </row>
     <row r="141">
       <c r="A141">
-        <v>2050458499572</v>
+        <v>2050458500209</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="142">
       <c r="A142">
-        <v>2050458499916</v>
+        <v>2050458499572</v>
       </c>
       <c r="B142">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143">
-        <v>2050458499626</v>
+        <v>2050458499916</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="144">
       <c r="A144">
-        <v>2050458500094</v>
+        <v>2050458499626</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -1553,7 +1553,7 @@
     </row>
     <row r="145">
       <c r="A145">
-        <v>2050458499992</v>
+        <v>2050458500094</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -1561,63 +1561,79 @@
     </row>
     <row r="146">
       <c r="A146">
-        <v>2050458500186</v>
+        <v>2050458499992</v>
       </c>
       <c r="B146">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147">
-        <v>2050458499824</v>
+        <v>2050458500186</v>
       </c>
       <c r="B147">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="148">
       <c r="A148">
-        <v>2050458499596</v>
+        <v>2050458499824</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="149">
       <c r="A149">
-        <v>2050458499435</v>
+        <v>2050458499596</v>
       </c>
       <c r="B149">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150">
-        <v>2050458499787</v>
+        <v>2050458499435</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="151">
       <c r="A151">
-        <v>2050458500308</v>
+        <v>2050458499787</v>
       </c>
       <c r="B151">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152">
+        <v>2050458500124</v>
+      </c>
+      <c r="B152">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>2050458500308</v>
+      </c>
+      <c r="B153">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
         <v>2050458500049</v>
       </c>
-      <c r="B152">
+      <c r="B154">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B152"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B154"/>
   </ignoredErrors>
 </worksheet>
 </file>